--- a/docs/triton-learning/cards/triton-lesson-01-vector-add-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-01-vector-add-technical-qa.xlsx
@@ -36,15 +36,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么 load mask 不能自动保护归约？</t>
+          <t xml:space="preserve">Triton kernel 先用 tl.load 的 mask 屏蔽尾块越界位置，再对加载结果做 sum 或 max 归约。为什么仍需处理无效位置的值，不能只依靠 load mask？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：load mask 关闭读取，但归约仍会看到保留下来的逻辑位置。
-• [T#B#输入]：false lane 没有消失；没有替代值时，其值可能未定义。
-• [T#B#合并]：归约把这些位置合并进结果，无效值因而可能污染有效输出。
-[T#B,!c47f17#边界]：应在归约前处理无效值；最后的 store mask 不能修复已污染的结果。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：load mask 保证无效地址不被读取，却不会把无效逻辑位置从结果 tensor 中删除；后续归约仍会合并这些位置的值。
+• [T#B#问题如何产生]：假设四个局部位置只有前两个有效。load 后仍有四个值；若后两个未定义，直接对四个值求和或求最大值，就可能污染本来有效的归约结果。
+• [T#B#归约前处理]：应在归约前把无效位置设置为适合该运算的值。例如求和用 0，使无效项不增加总和；求最大值可用负无穷，使它不竞争最大值。
+[T#B,!c47f17#边界]：最后的 store mask 只能控制结果写到哪里，不能从已污染的归约结果中撤销无效项的影响。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -61,13 +61,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">store mask 为 false 时，目标值怎样？</t>
+          <t xml:space="preserve">Triton kernel 对一个合法输出地址执行 tl.store，但该位置的 mask 为 false。这个位置会被写成零、写成未定义值，还是保留原值？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不写入；合法目标地址原有什么值，就保留什么值。
-[T#B,!c47f17#边界]：不等于写入零；mask 为 false 只表示这个位置没有写入副作用。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：该位置不发生写入，输出内存中原来是什么值，就继续保留什么值。
+• [T#B#具体例子]：假设写回前输出是 \[7, 8\]，待写入值是 \[1, 2\]，store mask 是 \[True, False\]，写回后输出为 \[1, 8\]。
+• [T#B#与 load 的区别]：masked load 需要产生一个局部结果，因此要考虑 false 位置的替代值；masked store 控制的是写入副作用，false 位置没有“写入替代值”这一步。
+[T#B,!c47f17#边界]：若输出缓冲区此前未初始化，保留原值也不代表得到可用结果；不能把“没有写”当作“已经写零”。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -84,14 +86,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">constexpr 参数能跨 launch 变化吗？</t>
+          <t xml:space="preserve">Triton 向量 kernel 将 BLOCK_SIZE 声明为 tl.constexpr，并用它构造块内 offsets。是否必须在源码里永远写死一个值，还是不同 kernel launch 可以选择不同值？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：可以；固定的范围是某一次 kernel 特化。
-• [T#B#变化范围]：不同 launch 可以选择不同 Python 整数，例如不同 BLOCK_SIZE。
-[T#B,!c47f17#边界]：本次特化所需的值必须在编译该版本前确定，不能等执行时再改变。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不同 launch 可以选择不同的 BLOCK_SIZE；tl.constexpr 要求的是某一次编译特化中的值固定，而不是整个程序生命周期都只能用一个值。
+• [T#B#固定在哪里]：编译器在生成这一版本的 kernel 时，需要知道 BLOCK_SIZE，才能确定块级表达式的形状和相关编译决策。
+• [T#B#怎样变化]：Python wrapper 可以在本次 launch 传入 256，下次传入 512；两次调用分别使用与该取值相匹配的特化。
+[T#B,!c47f17#边界]：不能让同一次正在执行的特化根据运行时 tensor 值改变 BLOCK_SIZE。需要区分 launch 前选配置与 kernel 执行时改变常量。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -108,14 +111,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">什么时候需要 callable grid？</t>
+          <t xml:space="preserve">启动 Triton 向量 kernel 时，program 数需要按输入长度和 BLOCK_SIZE 计算。什么情况下应使用 lambda META: ... 形式的 callable grid，而不是提前算好的 tuple grid？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：grid 依赖 Triton 随后绑定的 meta-parameters 时，需要延后计算。
-• [T#B#时机]：先绑定本次配置，再用该配置计算 program 数。
-[T#B,!c47f17#边界]：wrapper 已确定所需参数时，tuple grid 即可；输入尺寸会变化本身不是充分理由。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：当 grid 依赖的配置要等 Triton 绑定本次 meta-parameters 后才确定时，用 callable grid 延后计算。
+• [T#B#配置尚未确定]：例如 autotune 正在选择 BLOCK_SIZE，grid 也必须跟随当前候选配置变化。callable grid 接收本次 META，再据此计算覆盖输入所需的 program 数。
+• [T#B#配置已经确定]：如果 wrapper 已知道输入长度 N 和本次 BLOCK_SIZE，就可以提前计算 triton.cdiv(N, BLOCK_SIZE)，并作为 tuple grid 传入。
+[T#B,!c47f17#边界]：输入长度每次不同，并不自动要求 callable grid；关键是计算 grid 所需的值在什么时候才能确定。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -132,14 +136,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCK_SIZE 就是硬件线程数吗？</t>
+          <t xml:space="preserve">在 Triton 向量 kernel 中，tl.arange(0, BLOCK_SIZE) 为一个 program 构造块内位置。BLOCK_SIZE 是否就是这个 program 使用的 GPU 硬件线程数？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不是；它描述当前块级表达式中的逻辑位置数。
-• [T#B#层次]：program instance 处理 block tensor，编译器将逻辑操作映射到实际 threads/warps。
-[T#B,!c47f17#边界]：BLOCK_SIZE=4 不能直接推出启动了四个硬件线程。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不是。这里 BLOCK_SIZE 决定逻辑 block tensor 中有多少个元素位置，不能直接当成实际线程数量。
+• [T#B#program 层]：一个 program instance 执行一份块级 kernel，对这些逻辑位置进行加载、运算和写回。
+• [T#B#硬件层]：编译器再把块级操作映射到 GPU 的线程和 warp；逻辑元素的组织与硬件执行资源的组织是不同层次。
+[T#B,!c47f17#边界]：例如 BLOCK_SIZE=4 只说明 arange 产生四个逻辑位置，不能据此断言 GPU 启动了四个线程。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -156,14 +161,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">非连续输入为何不能直接用 ptr+offset？</t>
+          <t xml:space="preserve">一个 Triton 一维向量 kernel 用 ptr + offsets 读取元素。若 wrapper 开始接受每隔一个元素取一次的切片等非连续输入，为什么仅删除连续性检查还不够？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：ptr+offset 假设相邻逻辑元素在相邻存储位置。
-• [T#B#地址映射]：一维 stride 不为 1 时，地址要体现 ptr + offset * stride。
-[T#B,!c47f17#边界]：放宽 wrapper 的连续性检查不会自动修正 kernel 的地址计算。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：ptr + offsets 默认相邻逻辑元素也位于相邻存储位置。非连续一维 view 的逻辑索引必须先乘以 stride，才能对应正确地址。
+• [T#B#stride 的含义]：这里 stride 是相邻两个逻辑元素在底层存储中相隔的元素数，不是字节数。stride 为 2 时，逻辑位置 1 应读取基址之后的第 2 个元素位置。
+• [T#B#地址计算]：kernel 需要接收该输入的 stride，并按 ptr + offsets * stride 生成指针；否则仍会读取连续存储中的元素，得到错误数据。
+[T#B,!c47f17#边界]：wrapper 的接口范围必须与 kernel 的地址实现一致。放宽校验只能允许数据进入，不能自动改变实际访存方式。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -180,16 +186,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有效 GB/s 上升能证明带宽优化吗？</t>
+          <t xml:space="preserve">比较向量 kernel 的整块输入与稍长的尾块输入时，报告的“有效 GB/s”反而升高了。仅凭这个指标，能否认定 GPU 的实际 DRAM 带宽或 kernel 优化效果提高？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；有效 GB/s 是有效字节数与测量时间的比值。
-• [T#B#比值变化]：尾块比较中，有效元素数略增，而测得时间可能相同或落入较低档位。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。有效 GB/s 用算法规定的有效读写字节数除以测得耗时，指标升高可能只是工作量与测量时间的比值变化。
+• [T#B#符号定义]：令 N_exact、N_tail 分别表示整块和尾块用例的有效元素数，t_exact、t_tail 表示测得耗时，G 表示有效 GB/s。两组用例每个元素计入相同有效字节数时，有如下关系。
 [E##\frac{G_{\mathrm{tail}}}{G_{\mathrm{exact}}}=\frac{N_{\mathrm{tail}}}{N_{\mathrm{exact}}}\frac{t_{\mathrm{exact}}}{t_{\mathrm{tail}}}]
-• [T#B#因果判断]：分子增加或分母降低都能推高有效 GB/s，不能单凭这个变化归因于 GPU 优化。
-[T#B,!c47f17#边界]：上式按每元素有效字节数相同推导；该指标不等于实际 DRAM 流量或物理带宽。</t>
+• [T#B#如何解读]：尾块用例多几个有效元素，而两次时间恰好相同，分子变大就会让有效 GB/s 上升；测量波动使尾块时间更短也会产生同样现象。
+[T#B,!c47f17#边界]：有效字节数不是硬件实际传输的 DRAM 字节数。没有对应的受控测量或硬件证据，不能把比值上升直接解释为物理带宽增加或已证明的 GPU 优化。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -206,13 +212,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">do_bench(rep=100) 的 100 指什么？</t>
+          <t xml:space="preserve">使用 Triton 3.7.1 的 triton.testing.do_bench 测量一个很短的 GPU kernel，并设置 rep=100。这个 100 控制什么，是否会把一次 kernel 调用的计时间隔拉长到 100 ms？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：总采样预算约 100 ms。
-[T#B,!c47f17#边界]：不表示一次 kernel 会持续计时 100 ms，也不会把它原本很短的计时间隔拉长。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：rep=100 表示约 100 ms 的总采样预算，不表示某一次 kernel 调用要被连续计时 100 ms。
+• [T#B#总预算]：增加预算主要是在整轮测量中投入更多采样时间；被测 kernel 每次执行原本有多短，并不会因此自动变长。
+• [T#B#为什么要区分]：若担心单次 kernel 太短、测量分辨能力不足，仅增加总采样预算并不等于延长每一个计时间隔。
+[T#B,!c47f17#边界]：把多次调用放进同一个计时窗口后再求平均，是另一种测量设计，不能与 rep 的含义混为一谈。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -229,15 +237,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">批量平均时间能直接替代单次结果吗？</t>
+          <t xml:space="preserve">GPU 向量 kernel 单次耗时很短。若改为在同一个窗口内连续调用多次，再用总时间除以调用次数，所得平均延迟能直接替代原来的单次调用测量吗？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能直接替代；测量场景可能已经改变。
-• [T#B#场景变化]：批量连续调用可能改变缓存状态与发射方式。
-• [T#B#指标含义]：总时间除以次数，只得到这个批量场景的平均值。
-[T#B,!c47f17#边界]：应分别声明单次与批量的测量口径，不能把更平滑的结果当成原指标的更精确版本。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能直接替代。它测得的是连续批量执行场景中的每次平均成本，执行条件可能已经不同于原来的单次调用。
+• [T#B#为什么有帮助]：把多次执行合在一个窗口中，可以延长被测时间，减小极短窗口对观察结果的影响。
+• [T#B#为什么不是同一指标]：连续调用可能改变缓存状态、调用间间隔和发射方式。总时间除以次数会把这些批量场景的效果一起平均进去。
+[T#B,!c47f17#边界]：应分别说明两种结果的测量方式和适用场景。批量结果更平滑，不等于它天然就是原单次指标的更精确版本。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -254,14 +262,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">发现反证阈值不合适，原预测怎样判？</t>
+          <t xml:space="preserve">一项 GPU 尾块性能实验事先规定：延迟变化超过 5% 就判为不支持原预测。数据触发了该条件，之后才发现 5% 可能小于当前计时方法可分辨的变化。应怎样报告原实验结论？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先按事前规则报告结果，再说明阈值缺陷并改进后续实验。
-• [T#B#保留原判定]：原条件已被数据触发时，不能事后放宽标准，把结果改说成支持预测。
-[T#B,!c47f17#边界]：阈值低于测量可分辨能力属于方法限制，应单独说明，不抹去原判定过程。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：仍应按事先约定报告“原反证条件被触发”，并另行说明测量方法的限制；不能事后改标准，把同一结果重新称为支持原预测。
+• [T#B#保留原判定]：事前标准记录了原本准备用什么数据判断预测。看到结果后放宽标准，会失去这次检验的可追溯性。
+• [T#B#收紧实际结论]：阈值小于可分辨变化，说明现有测量可能不足以支持可靠的物理性能判断。因此要同时报告原规则下的结果与这个方法局限。
+• [T#B#改进后续实验]：重新设计更适合测量能力的标准与计时方法，再用新实验检验预测；新标准用于新的检验。
+[T#B,!c47f17#边界]：保留原判定不等于已经证实某个 GPU 机制，也不要求把受分辨率限制的数据解释得过于确定。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -278,15 +288,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">masked-out 访存是被优化掉的吗？</t>
+          <t xml:space="preserve">Triton 向量 kernel 的尾块用 mask 关闭越界位置的 tl.load/tl.store。为什么这些位置没有访存：GPU 先访问再消除结果，还是从执行条件上就不访问？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它本来就是条件访存；predicate 为 false 时，该 lane 不执行对应地址的读写。
-• [T#B#执行机制]：mask 参与访存的执行条件，不是先无条件访问，再把结果撤销。
-• [T#B#物理层次]：active lane 的访问仍按硬件事务粒度传输，不能由有效 lane 数直接得到实际流量。
-[T#B,!c47f17#边界]：地址、谓词和调度成本仍可能存在；尾部 program 不因此变成零开销。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：访存从一开始就是有条件的：对应 predicate 为 false 时，该逻辑位置不会执行所指定地址的读取或写入。
+• [T#B#执行条件]：在已核验的这份 kernel 中，底层 load/store 带有谓词条件。false 位置不是“先无条件访问，再由优化器撤销”，而是访存条件不成立。
+• [T#B#物理事务]：其他有效位置的请求仍按 GPU 的内存事务粒度合并和传输。因此屏蔽了几个逻辑位置，并不意味着实际 DRAM 流量必定减少同样数量的字节。
+[T#B,!c47f17#边界]：生成地址、计算谓词及调度这个 program 仍可能有成本。mask 关闭访存，不代表尾块没有执行开销。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-01-vector-add-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-01-vector-add-technical-qa.xlsx
@@ -43,13 +43,13 @@
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：load mask 保证无效地址不被读取，却不会把无效逻辑位置从结果 tensor 中删除；后续归约仍会合并这些位置的值。
 • [T#B#问题如何产生]：假设四个局部位置只有前两个有效。load 后仍有四个值；若后两个未定义，直接对四个值求和或求最大值，就可能污染本来有效的归约结果。
-• [T#B#归约前处理]：应在归约前把无效位置设置为适合该运算的值。例如求和用 0，使无效项不增加总和；求最大值可用负无穷，使它不竞争最大值。
+• [T#B#归约前处理]：应在归约前把无效位置设成不改变该归约结果的值，即该运算的单位元：求和用 0，求最大值用负无穷（同理，乘积用 1、求最小值用正无穷）；通常直接作为 tl.load 的 other 填入。
 [T#B,!c47f17#边界]：最后的 store mask 只能控制结果写到哪里，不能从已污染的归约结果中撤销无效项的影响。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">屏蔽读取 → 位置仍在 → 归约仍用值</t>
+          <t xml:space="preserve">屏蔽读取 → 位置仍在 → 归约前填单位元</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,50 +61,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton kernel 对一个合法输出地址执行 tl.store，但该位置的 mask 为 false。这个位置会被写成零、写成未定义值，还是保留原值？</t>
+          <t xml:space="preserve">Triton 条件写回 kernel 的尾块中，offsets 可能越过长度 N。load 用 mask=offsets &lt; N、other=-inf 读入 x；store 的 mask 只写 x &gt; threshold，靠 -inf 通不过这个比较来挡住越界 lane。如果之后把写回条件改成 x &lt; threshold，越界 lane 会怎样？store 的 mask 应怎样构造，才能不论比较条件怎样变都不写越界地址？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：该位置不发生写入，输出内存中原来是什么值，就继续保留什么值。
-• [T#B#具体例子]：假设写回前输出是 \[7, 8\]，待写入值是 \[1, 2\]，store mask 是 \[True, False\]，写回后输出为 \[1, 8\]。
-• [T#B#与 load 的区别]：masked load 需要产生一个局部结果，因此要考虑 false 位置的替代值；masked store 控制的是写入副作用，false 位置没有“写入替代值”这一步。
-[T#B,!c47f17#边界]：若输出缓冲区此前未初始化，保留原值也不代表得到可用结果；不能把“没有写”当作“已经写零”。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：改成 x &lt; threshold 后，-inf 对任何有限阈值都满足条件，越界 lane 会通过 mask 去写非法地址。稳健写法是把边界条件与数值条件取逻辑与：write_mask = (offsets &lt; N) &amp; condition，让边界谓词单独负责排除越界地址，数值条件只决定要不要写。
+• [T#B#原推导为何成立]：在 x &gt; threshold 下，-inf 不会大于任何有限阈值，越界 lane 确实不会被写回；这个推导本身没错，只是安全性依赖于填充值与比较方向的特定关系。
+• [T#B#为何要显式合并]：other 只是 load 给未读取位置的替代数值，不是 tl.store 会自动继承的边界保护。比较方向或阈值一变（例如改成 x &lt; threshold，或 x &gt;= threshold 而阈值恰为 -inf），sentinel 就可能通过条件；显式合并后，越界位置的 mask 恒为 false。
+[T#B,!c47f17#边界]：other 仍然有用：未读取位置参与后续计算（例如归约）时取什么值由它决定；但它不能代替写回时的边界条件。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false → 无写入副作用</t>
+          <t xml:space="preserve">sentinel 只对特定比较成立；边界谓词单独负责越界</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 · L01 日志：load/store mask 对照</t>
+          <t xml:space="preserve">Triton 3.7.1 · L01 日志：条件写回的边界 mask</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 向量 kernel 将 BLOCK_SIZE 声明为 tl.constexpr，并用它构造块内 offsets。是否必须在源码里永远写死一个值，还是不同 kernel launch 可以选择不同值？</t>
+          <t xml:space="preserve">Triton 向量 kernel 把 BLOCK_SIZE 声明为 tl.constexpr，用它构造 tl.arange(0, BLOCK_SIZE)；wrapper 按输入长度从 256、512、1024 中挑一个值传入。tl.constexpr 要求的“固定”是在什么范围内固定？每换到一个新值，第一次 launch 时会发生什么？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不同 launch 可以选择不同的 BLOCK_SIZE；tl.constexpr 要求的是某一次编译特化中的值固定，而不是整个程序生命周期都只能用一个值。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：只要求在一次编译特化内固定：不同 launch 可以传入不同的 Python 整数；每个新值第一次使用时，Triton 会 JIT 编译出与之匹配的特化，之后同一取值复用已编译的版本。
 • [T#B#固定在哪里]：编译器在生成这一版本的 kernel 时，需要知道 BLOCK_SIZE，才能确定块级表达式的形状和相关编译决策。
-• [T#B#怎样变化]：Python wrapper 可以在本次 launch 传入 256，下次传入 512；两次调用分别使用与该取值相匹配的特化。
-[T#B,!c47f17#边界]：不能让同一次正在执行的特化根据运行时 tensor 值改变 BLOCK_SIZE。需要区分 launch 前选配置与 kernel 执行时改变常量。</t>
+• [T#B#怎样变化]：wrapper 本次传 256、下次传 512 都合法；两次调用分别使用与该取值匹配的特化。
+[T#B,!c47f17#边界]：值必须在 launch 前就是确定的 Python 整数，不能等 kernel 执行时再按运行时 tensor 的值决定；每个新值都要付一次编译，所以候选值宜少。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">特化内固定；launch 间可选</t>
+          <t xml:space="preserve">特化内固定；新值首用即编译</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 · L01 日志：constexpr 的取值范围</t>
+          <t xml:space="preserve">Triton 3.7.1 · L01 日志：constexpr 的取值范围、首次调用含 JIT</t>
         </is>
       </c>
     </row>
@@ -136,13 +136,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 Triton 向量 kernel 中，tl.arange(0, BLOCK_SIZE) 为一个 program 构造块内位置。BLOCK_SIZE 是否就是这个 program 使用的 GPU 硬件线程数？</t>
+          <t xml:space="preserve">Triton 向量 kernel 用 tl.program_id(0) 确定当前块，用 tl.arange(0, BLOCK_SIZE) 构造块内位置，再用 tl.load/tl.store 访存。BLOCK_SIZE 是哪一层的数量？它和这个 program 实际使用的 GPU threads/warps 是什么关系？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不是。这里 BLOCK_SIZE 决定逻辑 block tensor 中有多少个元素位置，不能直接当成实际线程数量。
-• [T#B#program 层]：一个 program instance 执行一份块级 kernel，对这些逻辑位置进行加载、运算和写回。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：BLOCK_SIZE 是 block-tensor 层的逻辑位置数，即一个 program 的块级 tensor 有多少个元素位置；实际用多少 threads/warps 由编译器映射决定，二者没有一一对应，不能把 BLOCK_SIZE 当成线程数。
+• [T#B#分层]：tl.program_id 位于 program-instance 层，表示当前是 grid 中的第几个 program；tl.arange 与 tl.load/tl.store 位于 block-tensor 层，对整块逻辑位置逐 lane 运算和访存。
 • [T#B#硬件层]：编译器再把块级操作映射到 GPU 的线程和 warp；逻辑元素的组织与硬件执行资源的组织是不同层次。
 [T#B,!c47f17#边界]：例如 BLOCK_SIZE=4 只说明 arange 产生四个逻辑位置，不能据此断言 GPU 启动了四个线程。</t>
         </is>
@@ -167,7 +167,7 @@
       <c r="B7" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：ptr + offsets 默认相邻逻辑元素也位于相邻存储位置。非连续一维 view 的逻辑索引必须先乘以 stride，才能对应正确地址。
-• [T#B#stride 的含义]：这里 stride 是相邻两个逻辑元素在底层存储中相隔的元素数，不是字节数。stride 为 2 时，逻辑位置 1 应读取基址之后的第 2 个元素位置。
+• [T#B#stride 的含义]：这里 stride 是相邻两个逻辑元素在底层存储中相隔的元素数，不是字节数。stride 为 2 时，逻辑位置 i 的存储偏移是 i × 2：逻辑位置 1 应读 base\[2\]，只做 ptr + offsets 却会读到 base\[1\]。
 • [T#B#地址计算]：kernel 需要接收该输入的 stride，并按 ptr + offsets * stride 生成指针；否则仍会读取连续存储中的元素，得到错误数据。
 [T#B,!c47f17#边界]：wrapper 的接口范围必须与 kernel 的地址实现一致。放宽校验只能允许数据进入，不能自动改变实际访存方式。</t>
         </is>
@@ -186,15 +186,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">比较向量 kernel 的整块输入与稍长的尾块输入时，报告的“有效 GB/s”反而升高了。仅凭这个指标，能否认定 GPU 的实际 DRAM 带宽或 kernel 优化效果提高？</t>
+          <t xml:space="preserve">比较向量 kernel 的整块输入与稍长的尾块输入时，尾块的“有效 GB/s”反而更高。写出两者有效 GB/s 之比与有效元素数、测得耗时的关系，并据此说明这个比值上升可能来自哪里。</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。有效 GB/s 用算法规定的有效读写字节数除以测得耗时，指标升高可能只是工作量与测量时间的比值变化。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：比值等于有效元素数之比乘以耗时的反比：尾块多出几个有效元素而耗时相同，或尾块的测得耗时因测量波动落到更低的计时档位，比值就会上升。这只是工作量与测得时间的比值变化，不能据此认定 DRAM 带宽或 kernel 优化提高。
 • [T#B#符号定义]：令 N_exact、N_tail 分别表示整块和尾块用例的有效元素数，t_exact、t_tail 表示测得耗时，G 表示有效 GB/s。两组用例每个元素计入相同有效字节数时，有如下关系。
 [E##\frac{G_{\mathrm{tail}}}{G_{\mathrm{exact}}}=\frac{N_{\mathrm{tail}}}{N_{\mathrm{exact}}}\frac{t_{\mathrm{exact}}}{t_{\mathrm{tail}}}]
-• [T#B#如何解读]：尾块用例多几个有效元素，而两次时间恰好相同，分子变大就会让有效 GB/s 上升；测量波动使尾块时间更短也会产生同样现象。
 [T#B,!c47f17#边界]：有效字节数不是硬件实际传输的 DRAM 字节数。没有对应的受控测量或硬件证据，不能把比值上升直接解释为物理带宽增加或已证明的 GPU 优化。</t>
         </is>
       </c>
@@ -212,96 +211,97 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">使用 Triton 3.7.1 的 triton.testing.do_bench 测量一个很短的 GPU kernel，并设置 rep=100。这个 100 控制什么，是否会把一次 kernel 调用的计时间隔拉长到 100 ms？</t>
+          <t xml:space="preserve">fp32 向量加法 z = x + y 处理 N 个元素。按算法最低数据流量，每个元素要搬运多少字节、做几次运算？据此说明它为什么通常受内存带宽限制。</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：rep=100 表示约 100 ms 的总采样预算，不表示某一次 kernel 调用要被连续计时 100 ms。
-• [T#B#总预算]：增加预算主要是在整轮测量中投入更多采样时间；被测 kernel 每次执行原本有多短，并不会因此自动变长。
-• [T#B#为什么要区分]：若担心单次 kernel 太短、测量分辨能力不足，仅增加总采样预算并不等于延长每一个计时间隔。
-[T#B,!c47f17#边界]：把多次调用放进同一个计时窗口后再求平均，是另一种测量设计，不能与 rep 的含义混为一谈。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：每个元素读 x、读 y、写 z 各 4 字节，共 12 字节，却只做 1 次加法：计算极少、数据搬运很多，耗时主要由内存读写决定，所以通常受带宽限制。benchmark 有效带宽公式里的系数 3 就是这两读一写。
+[E##\text{GB/s}=\frac{3\times N\times\text{element\_size}\times10^{-9}}{\text{ms}\times10^{-3}}]
+• [T#B#算一笔]：每 12 字节只对应 1 次加法；算术单元很快就能算完这些加法，大部分时间花在等数据读写上。
+• [T#B#“有效”的含义]：公式按算法最低数据量计字节，不是硬件计数器测得的 DRAM 流量；缓存、写策略和其他内部流量都没有计入。
+[T#B,!c47f17#边界]：带宽受限描述的是输入足够大时的稳态：小输入时 kernel launch 和固定开销占主导，有效 GB/s 偏低且容易波动。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">总预算 ≠ 单次间隔</t>
+          <t xml:space="preserve">两读一写 12 B 对 1 次加法 → 带宽受限；系数 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 · L01 日志：do_bench 采样口径</t>
+          <t xml:space="preserve">L01 日志：带宽受限与有效带宽</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GPU 向量 kernel 单次耗时很短。若改为在同一个窗口内连续调用多次，再用总时间除以调用次数，所得平均延迟能直接替代原来的单次调用测量吗？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中用 triton.testing.do_bench 测一个只需几微秒的向量 kernel，单次计时窗口太短。把 rep=100 调大，改变的是什么？若改为在一个样本里连续调用 100 次、再用总时间除以 100，这个平均值测到的又是什么？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能直接替代。它测得的是连续批量执行场景中的每次平均成本，执行条件可能已经不同于原来的单次调用。
-• [T#B#为什么有帮助]：把多次执行合在一个窗口中，可以延长被测时间，减小极短窗口对观察结果的影响。
-• [T#B#为什么不是同一指标]：连续调用可能改变缓存状态、调用间间隔和发射方式。总时间除以次数会把这些批量场景的效果一起平均进去。
-[T#B,!c47f17#边界]：应分别说明两种结果的测量方式和适用场景。批量结果更平滑，不等于它天然就是原单次指标的更精确版本。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：调大 rep 只会增加样本数，每个样本仍只包住一次调用，窗口不会变长；批量调用确实拉长了窗口，但测到的是连续执行时每次调用的平均成本，缓存状态和发射方式都已不同于原来的单次调用，是另一种指标。
+• [T#B#采样预算]：rep 的单位是毫秒，表示总共采样多久；它只决定样本数，每个正式样本仍用一对 GPU event 包住一次 fn()。
+• [T#B#批量改变了什么]：do_bench 在每个正式样本前清一次 L2 cache；100 次调用算作一个样本时，只有第一次调用前清过缓存，后续调用可能读到前一次留在缓存里的数据，连续发射的方式也与单次调用不同。
+[T#B,!c47f17#边界]：两种结果都可以报告，但要分别说明测量方式与适用场景；批量结果更平滑，不等于它是原单次指标的更精确版本。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">窗口变长，也可能换了被测场景</t>
+          <t xml:space="preserve">rep 只加样本；批量拉长窗口也换了场景</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">L01 日志：批量计时与单次计时对照</t>
+          <t xml:space="preserve">Triton 3.7.1 · L01 日志：do_bench 采样口径与批量计时</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">一项 GPU 尾块性能实验事先规定：延迟变化超过 5% 就判为不支持原预测。数据触发了该条件，之后才发现 5% 可能小于当前计时方法可分辨的变化。应怎样报告原实验结论？</t>
+          <t xml:space="preserve">用 time.perf_counter() 在调用一次 Triton kernel wrapper 的前后各取一次时间，把差值当作 kernel 耗时。这个读数会漏算什么、又可能多算什么？应怎样正确计时（以 Triton 3.7.1 的 do_bench 为参照）？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：仍应按事先约定报告“原反证条件被触发”，并另行说明测量方法的限制；不能事后改标准，把同一结果重新称为支持原预测。
-• [T#B#保留原判定]：事前标准记录了原本准备用什么数据判断预测。看到结果后放宽标准，会失去这次检验的可追溯性。
-• [T#B#收紧实际结论]：阈值小于可分辨变化，说明现有测量可能不足以支持可靠的物理性能判断。因此要同时报告原规则下的结果与这个方法局限。
-• [T#B#改进后续实验]：重新设计更适合测量能力的标准与计时方法，再用新实验检验预测；新标准用于新的检验。
-[T#B,!c47f17#边界]：保留原判定不等于已经证实某个 GPU 机制，也不要求把受分辨率限制的数据解释得过于确定。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：kernel launch 只是把工作排进 GPU stream，wrapper 返回时 GPU 可能还没算完，CPU 计时会漏掉这段执行；首次调用还会触发 JIT 编译，把编译时间多算进去。正确做法是先预热，再在开始和停止计时前同步 GPU，或改用 GPU event 计时。
+• [T#B#漏算]：CPU 可能只等到 kernel 被提交就停止计时。返回 output 本身是安全的：同一 stream 上依赖它的后续操作仍按顺序执行，只是计时读数偏小。
+• [T#B#多算]：每种配置（例如新的 BLOCK_SIZE）第一次使用时要编译对应特化，之后复用缓存，所以首次调用不能代表稳态性能。
+• [T#B#手写计时]：先跑过预热调用；开始计时前和停止计时前各调用一次 torch.cuda.synchronize()。
+• [T#B#do_bench]：先调用并同步一次 fn()，编译不进入正式样本；再预热，并在每个正式样本前清 L2、用一对 GPU event 包住一次调用。
+[T#B,!c47f17#边界]：这样测到的是稳态运行性能，不是首次调用延迟；编译开销依然存在，只是不计入正式样本。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原规则判定；新发现改下一次</t>
+          <t xml:space="preserve">launch 只入队 → 同步或 event；首次含 JIT → 预热</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">L01 日志：尾块实验的反证标准复盘</t>
+          <t xml:space="preserve">Triton 3.7.1 · L01 日志：异步执行与计时</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 向量 kernel 的尾块用 mask 关闭越界位置的 tl.load/tl.store。为什么这些位置没有访存：GPU 先访问再消除结果，还是从执行条件上就不访问？</t>
+          <t xml:space="preserve">Triton 向量 kernel 的尾块用 mask 关闭越界位置的 tl.load/tl.store。有人把这些位置没有访存解释成“GPU 或编译器把冗余访存优化掉了”。在 Triton 3.7.1 为 NVIDIA GPU 生成的 PTX 里，这些访存为什么没有发生？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：访存从一开始就是有条件的：对应 predicate 为 false 时，该逻辑位置不会执行所指定地址的读取或写入。
-• [T#B#执行条件]：在已核验的这份 kernel 中，底层 load/store 带有谓词条件。false 位置不是“先无条件访问，再由优化器撤销”，而是访存条件不成立。
-• [T#B#物理事务]：其他有效位置的请求仍按 GPU 的内存事务粒度合并和传输。因此屏蔽了几个逻辑位置，并不意味着实际 DRAM 流量必定减少同样数量的字节。
-[T#B,!c47f17#边界]：生成地址、计算谓词及调度这个 program 仍可能有成本。mask 关闭访存，不代表尾块没有执行开销。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为访存本身就是有条件执行的：生成的 PTX 用 guard predicate 修饰 load/store（形如 @%p1 ld.global），predicate 为 false 的 lane 从一开始就不执行对应地址的读写，不是先访问、再由优化撤销。
+• [T#B#执行条件]：mask 被编译成访存指令的执行条件；尾块中越界 lane 的谓词为 false，对应的读写根本不会执行。
+[T#B,!c47f17#边界]：predicate 只关掉 false lane 的访存：地址与谓词计算、program 调度仍有成本，有效 lane 的访存仍按硬件事务粒度进行。以上只在 NVIDIA PTX 上核对过，其他后端（如 AMD）的底层形式未核对。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">条件访存 ≠ 事后优化；有效字节 ≠ 物理事务</t>
+          <t xml:space="preserve">条件访存 ≠ 事后优化</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
